--- a/PMS.UI/wwwroot/temp/Call Summary.xlsx
+++ b/PMS.UI/wwwroot/temp/Call Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noman.yousaf\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9946784B-BB41-4012-9C72-87F005E14EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741B9847-E066-47AA-8AE4-3BC6F87BD0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>Name</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Unbillable Total</t>
   </si>
   <si>
-    <t>Shahid Rasheed</t>
-  </si>
-  <si>
     <t>Rafay Ahmad</t>
   </si>
   <si>
@@ -81,45 +78,27 @@
     <t>Daniyal Ahmad</t>
   </si>
   <si>
-    <t>Muzna Habib</t>
-  </si>
-  <si>
     <t>Furqan Ali</t>
   </si>
   <si>
     <t>Muhammad Tayyab</t>
   </si>
   <si>
-    <t>Rao Aosaf</t>
-  </si>
-  <si>
     <t>Moeez Zaheer</t>
   </si>
   <si>
     <t>Artza Sibgha</t>
   </si>
   <si>
-    <t>Mirza Khurram</t>
-  </si>
-  <si>
     <t>Nadia Saleem</t>
   </si>
   <si>
-    <t>Asad Ali</t>
-  </si>
-  <si>
     <t>Waqas Masih</t>
   </si>
   <si>
-    <t>Ayesha Shafique</t>
-  </si>
-  <si>
     <t>Ramsha Fatima</t>
   </si>
   <si>
-    <t>Sarmad Rahman</t>
-  </si>
-  <si>
     <t>Muhammad Sadaq</t>
   </si>
   <si>
@@ -132,27 +111,15 @@
     <t>Unaiza Zulfiqar</t>
   </si>
   <si>
-    <t>Saleem Khan</t>
-  </si>
-  <si>
-    <t>Sidratul Muntaha</t>
-  </si>
-  <si>
     <t>Umer Tufail</t>
   </si>
   <si>
-    <t>Nouman Khurshid</t>
-  </si>
-  <si>
     <t>Muhammad Kashif</t>
   </si>
   <si>
     <t>Murad Rathore</t>
   </si>
   <si>
-    <t>Saffi Rehman</t>
-  </si>
-  <si>
     <t>Ejaz Hassan</t>
   </si>
   <si>
@@ -165,9 +132,6 @@
     <t>Ali Akbar</t>
   </si>
   <si>
-    <t>Rumasa Yasir</t>
-  </si>
-  <si>
     <t>Muhammad Nouman</t>
   </si>
   <si>
@@ -189,15 +153,6 @@
     <t>Hasham Aslam</t>
   </si>
   <si>
-    <t>Awais Afzal</t>
-  </si>
-  <si>
-    <t>Abdullah Imtiaz</t>
-  </si>
-  <si>
-    <t>Mahad Khan</t>
-  </si>
-  <si>
     <t>Talha Waseem</t>
   </si>
   <si>
@@ -219,9 +174,6 @@
     <t>Touqeer Rehman</t>
   </si>
   <si>
-    <t>Sonia Shehzadi</t>
-  </si>
-  <si>
     <t>Abdullah Butt</t>
   </si>
   <si>
@@ -231,24 +183,15 @@
     <t>Adil Nabeel</t>
   </si>
   <si>
-    <t>Shumail Ahmed</t>
-  </si>
-  <si>
     <t>Zubair Aftab</t>
   </si>
   <si>
     <t>Khawaja Usama</t>
   </si>
   <si>
-    <t>Hassan Asad</t>
-  </si>
-  <si>
     <t>Danish Baig</t>
   </si>
   <si>
-    <t>Hira Khalid</t>
-  </si>
-  <si>
     <t>Ahmed Haasan</t>
   </si>
   <si>
@@ -298,6 +241,198 @@
   </si>
   <si>
     <t>Create Date</t>
+  </si>
+  <si>
+    <t>Abdul Moeez</t>
+  </si>
+  <si>
+    <t>Abdul Samad</t>
+  </si>
+  <si>
+    <t>Abdullah Arslan</t>
+  </si>
+  <si>
+    <t>Abdulrehman Tariq</t>
+  </si>
+  <si>
+    <t>Adeel Sadiq</t>
+  </si>
+  <si>
+    <t>Afshan Ali</t>
+  </si>
+  <si>
+    <t>Ahmad Khan</t>
+  </si>
+  <si>
+    <t>Ali Abbas</t>
+  </si>
+  <si>
+    <t>Ali Haider</t>
+  </si>
+  <si>
+    <t>Ali Khan</t>
+  </si>
+  <si>
+    <t>Ameer Hamza</t>
+  </si>
+  <si>
+    <t>Amna Khalid</t>
+  </si>
+  <si>
+    <t>Amna Mustafa</t>
+  </si>
+  <si>
+    <t>Arshian Khalid</t>
+  </si>
+  <si>
+    <t>Awais Younas</t>
+  </si>
+  <si>
+    <t>Ayoub Javed</t>
+  </si>
+  <si>
+    <t>Behzad Ahmed</t>
+  </si>
+  <si>
+    <t>Eleazar saleem</t>
+  </si>
+  <si>
+    <t>Fahad Rafiq</t>
+  </si>
+  <si>
+    <t>Ghias Haider</t>
+  </si>
+  <si>
+    <t>Haider Ali</t>
+  </si>
+  <si>
+    <t>Haifa Zahid</t>
+  </si>
+  <si>
+    <t>Hamas Dar</t>
+  </si>
+  <si>
+    <t>Hamza Butt</t>
+  </si>
+  <si>
+    <t>Hamza Zahid</t>
+  </si>
+  <si>
+    <t>Haris Haroon</t>
+  </si>
+  <si>
+    <t>Hasan Shafat</t>
+  </si>
+  <si>
+    <t>Husnain Aftab</t>
+  </si>
+  <si>
+    <t>Irfan Meraj</t>
+  </si>
+  <si>
+    <t>Jamal Akmal</t>
+  </si>
+  <si>
+    <t>Karoline Arif</t>
+  </si>
+  <si>
+    <t>Maryam Inam</t>
+  </si>
+  <si>
+    <t>Mehboob Yaqoob</t>
+  </si>
+  <si>
+    <t>Mohid Ali</t>
+  </si>
+  <si>
+    <t>Muaaz Sadiq</t>
+  </si>
+  <si>
+    <t>Muhammad Aliraza</t>
+  </si>
+  <si>
+    <t>Muhammad Din</t>
+  </si>
+  <si>
+    <t>Muhammad Haris</t>
+  </si>
+  <si>
+    <t>Muhammad Hassan</t>
+  </si>
+  <si>
+    <t>Muhammad Javed</t>
+  </si>
+  <si>
+    <t>Muhammad Shaukat</t>
+  </si>
+  <si>
+    <t>Mujtaba Shehzad</t>
+  </si>
+  <si>
+    <t>Muqeet Butt</t>
+  </si>
+  <si>
+    <t>Noshaba Haneef</t>
+  </si>
+  <si>
+    <t>Numan Latif</t>
+  </si>
+  <si>
+    <t>Osama Abaid</t>
+  </si>
+  <si>
+    <t>Philemoon Riaz</t>
+  </si>
+  <si>
+    <t>Raja Suleman</t>
+  </si>
+  <si>
+    <t>Rana Shujat</t>
+  </si>
+  <si>
+    <t>Rhea Khan</t>
+  </si>
+  <si>
+    <t>Rida Fatima</t>
+  </si>
+  <si>
+    <t>Ruby Talib</t>
+  </si>
+  <si>
+    <t>Salman Mehdi</t>
+  </si>
+  <si>
+    <t>Samar Khan</t>
+  </si>
+  <si>
+    <t>Sani Ali</t>
+  </si>
+  <si>
+    <t>Shavaiz Abbas</t>
+  </si>
+  <si>
+    <t>Shmoil Shoukat</t>
+  </si>
+  <si>
+    <t>Syed Adnan</t>
+  </si>
+  <si>
+    <t>Umair Asghar</t>
+  </si>
+  <si>
+    <t>Zahair Farooq</t>
+  </si>
+  <si>
+    <t>Zarbakht Ali</t>
+  </si>
+  <si>
+    <t>Zaryab Hussain</t>
+  </si>
+  <si>
+    <t>Zoya Raza</t>
+  </si>
+  <si>
+    <t>Zunaira Rehman</t>
   </si>
 </sst>
 </file>
@@ -616,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -634,7 +769,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -669,579 +804,579 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>45148</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4338</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1447</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>5951</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>49662</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5026</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1233</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1954</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>7421</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>31417</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4074</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>3796</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>8846</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>33378</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4985</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>32222</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>4216</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4966</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>30795</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4149</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1427</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>6771</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>32974</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2954</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>4356</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C9">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>32350</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>4410</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1766</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>6228</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>32703</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>4099</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1146</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>5345</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="C11">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>19135</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1406</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>2908</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>32443</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>4083</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1796</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>6128</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C13">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D13">
-        <v>32109</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>4281</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>2467</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>6921</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C14">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>21796</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>2361</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1193</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>3826</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>40172</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>4284</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>5779</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C16">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>33057</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>4054</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>934</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>5343</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C17">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D17">
-        <v>54370</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>5755</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>804</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>6804</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C18">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>31327</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>4103</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1250,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>5107</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1264,299 +1399,299 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C19">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="D19">
-        <v>33390</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2905</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>3367</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>32141</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>5162</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C21">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D21">
-        <v>32409</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>3559</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1324</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1731</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>5450</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C22">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D22">
-        <v>35341</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>4270</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>5447</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D23">
-        <v>41545</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>4085</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>1241</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1238</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>6910</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C24">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="D24">
-        <v>31235</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>5485</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1748</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>7373</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25">
         <v>33</v>
       </c>
-      <c r="C25">
-        <v>78</v>
-      </c>
       <c r="D25">
-        <v>38314</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>4165</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>687</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1922</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>6981</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>30667</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1813</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>6780</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C27">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="D27">
-        <v>32557</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>3149</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1565,13 +1700,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>1067</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1579,124 +1714,124 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>35029</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>3086</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>4762</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C29">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D29">
-        <v>33401</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>6908</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C30">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D30">
-        <v>32619</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2593</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>5270</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31">
         <v>39</v>
       </c>
-      <c r="C31">
-        <v>75</v>
-      </c>
       <c r="D31">
-        <v>37108</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>3855</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1705,13 +1840,13 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>631</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>4687</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -1719,264 +1854,264 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C32">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D32">
-        <v>31302</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>1062</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33">
         <v>41</v>
       </c>
-      <c r="C33">
-        <v>73</v>
-      </c>
       <c r="D33">
-        <v>32202</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>5230</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>2010</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>7731</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="D34">
-        <v>32863</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>2728</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>3618</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>6785</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35">
         <v>43</v>
       </c>
-      <c r="C35">
-        <v>73</v>
-      </c>
       <c r="D35">
-        <v>31295</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>3841</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>1170</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>5108</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C36">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D36">
-        <v>32328</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>4710</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>2950</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>8016</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C37">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>31156</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>2168</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>6784</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C38">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D38">
-        <v>35514</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>2203</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1576</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>4999</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C39">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D39">
-        <v>34489</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>4180</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1985,13 +2120,13 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>834</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>5091</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -1999,264 +2134,264 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C40">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D40">
-        <v>34232</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>3050</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>4415</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C41">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D41">
-        <v>36316</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>4660</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>5210</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="C42">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D42">
-        <v>32121</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>3459</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>4644</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="C43">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D43">
-        <v>33270</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>3762</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>1348</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>5455</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="C44">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D44">
-        <v>32609</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>3687</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>4293</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="C45">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D45">
-        <v>31023</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>2666</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>4278</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="C46">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D46">
-        <v>34126</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>3505</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>3916</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C47">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D47">
-        <v>13639</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1418</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2265,13 +2400,13 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>1603</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -2279,1049 +2414,1049 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C48">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D48">
-        <v>33822</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>5513</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>6760</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C49">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D49">
-        <v>35438</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>2809</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C50">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D50">
-        <v>35609</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>1377</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>5483</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C51">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D51">
-        <v>34109</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>2644</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>3089</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C52">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D52">
-        <v>32677</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D53">
-        <v>33628</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>4224</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>887</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>5571</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C54">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D54">
-        <v>9352</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C55">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D55">
-        <v>32528</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>4127</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="I55">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>4739</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D56">
-        <v>19671</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>2959</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>3169</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C57">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D57">
-        <v>31403</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>5203</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C58">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D58">
-        <v>27562</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>3243</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>4390</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C59">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D59">
-        <v>28630</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>3648</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>1321</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>5065</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C60">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D60">
-        <v>30261</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>1795</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>2548</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C61">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D61">
-        <v>32189</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>3741</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>729</v>
+        <v>0</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>5279</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C62">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D62">
-        <v>32329</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>6046</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>459</v>
+        <v>0</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>7497</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C63">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D63">
-        <v>31058</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>3751</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>2096</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>6065</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C64">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D64">
-        <v>33722</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C65">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D65">
-        <v>32255</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>4235</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>5767</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C66">
         <v>37</v>
       </c>
       <c r="D66">
-        <v>31115</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>4035</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>4371</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C67">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D67">
-        <v>32504</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>4555</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>7312</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C68">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D68">
-        <v>23842</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>4608</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>6127</v>
+        <v>0</v>
       </c>
       <c r="K68">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C69">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D69">
-        <v>15317</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>4455</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I69">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>5659</v>
+        <v>0</v>
       </c>
       <c r="K69">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C70">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D70">
-        <v>25477</v>
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>3771</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="K70">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C71">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D71">
-        <v>32265</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K71">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C72">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D72">
-        <v>47095</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>3751</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>4181</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C73">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D73">
-        <v>31554</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>2714</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>1428</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>4356</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C74">
         <v>30</v>
       </c>
       <c r="D74">
-        <v>32394</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>5202</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>1732</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="J74">
-        <v>7330</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C75">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D75">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1915</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>721</v>
+        <v>0</v>
       </c>
       <c r="J75">
-        <v>3327</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="C76">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D76">
-        <v>31981</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>4115</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>2777</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I76">
-        <v>853</v>
+        <v>0</v>
       </c>
       <c r="J76">
-        <v>7797</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C77">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D77">
-        <v>32707</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>4257</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>1038</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>1199</v>
+        <v>0</v>
       </c>
       <c r="J77">
-        <v>6535</v>
+        <v>0</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -3329,142 +3464,1717 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C78">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D78">
-        <v>18905</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>3513</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G78">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="H78">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I78">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="J78">
-        <v>4387</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="C79">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D79">
-        <v>21015</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>2357</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>3454</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C80">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D80">
-        <v>25375</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>4503</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I80">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="J80">
-        <v>4968</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C81">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D81">
-        <v>32502</v>
+        <v>0</v>
       </c>
       <c r="E81">
-        <v>4195</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>5787</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>196</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B82" t="s">
+        <v>69</v>
+      </c>
+      <c r="C82">
+        <v>24</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B83" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83">
+        <v>37</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B84" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84">
+        <v>50</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85">
+        <v>29</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B86" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B87" t="s">
+        <v>63</v>
+      </c>
+      <c r="C87">
+        <v>21</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B88" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88">
+        <v>30</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B89" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89">
+        <v>24</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B90" t="s">
+        <v>116</v>
+      </c>
+      <c r="C90">
+        <v>21</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B91" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91">
+        <v>14</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B92" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92">
+        <v>20</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93">
+        <v>27</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94">
+        <v>41</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95">
+        <v>29</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B96" t="s">
+        <v>120</v>
+      </c>
+      <c r="C96">
+        <v>28</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B97" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97">
+        <v>32</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B98" t="s">
+        <v>121</v>
+      </c>
+      <c r="C98">
+        <v>8</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B99" t="s">
+        <v>122</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100">
+        <v>26</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B101" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101">
+        <v>44</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B102" t="s">
+        <v>124</v>
+      </c>
+      <c r="C102">
+        <v>29</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B103" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103">
+        <v>35</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B104" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104">
+        <v>19</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B105" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105">
+        <v>24</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106">
+        <v>46</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B107" t="s">
+        <v>127</v>
+      </c>
+      <c r="C107">
+        <v>38</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B108" t="s">
+        <v>128</v>
+      </c>
+      <c r="C108">
+        <v>42</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B109" t="s">
+        <v>57</v>
+      </c>
+      <c r="C109">
+        <v>24</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B110" t="s">
+        <v>129</v>
+      </c>
+      <c r="C110">
+        <v>36</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B111" t="s">
+        <v>42</v>
+      </c>
+      <c r="C111">
+        <v>25</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B112" t="s">
+        <v>64</v>
+      </c>
+      <c r="C112">
+        <v>16</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113">
+        <v>27</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B114" t="s">
+        <v>130</v>
+      </c>
+      <c r="C114">
+        <v>27</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B115" t="s">
+        <v>28</v>
+      </c>
+      <c r="C115">
+        <v>30</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B116" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116">
+        <v>46</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B117" t="s">
+        <v>45</v>
+      </c>
+      <c r="C117">
+        <v>29</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B118" t="s">
+        <v>39</v>
+      </c>
+      <c r="C118">
+        <v>47</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B119" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119">
+        <v>39</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120">
+        <v>26</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121">
+        <v>41</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122">
+        <v>17</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123">
+        <v>17</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B124" t="s">
+        <v>134</v>
+      </c>
+      <c r="C124">
+        <v>32</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B125" t="s">
+        <v>52</v>
+      </c>
+      <c r="C125">
+        <v>29</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B126" t="s">
+        <v>135</v>
+      </c>
+      <c r="C126">
+        <v>27</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
